--- a/Data Files/Backoffce/GeraBlocoBCadastroCorretorData/RamosBlocoB.xlsx
+++ b/Data Files/Backoffce/GeraBlocoBCadastroCorretorData/RamosBlocoB.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20373"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\GeraBlocoBCadastroCorretorData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599E8C54-249A-4DD9-A327-3CE7FA627B7D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916209A6-F491-485A-9F80-937FC07AC91F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Ramos</t>
   </si>
@@ -52,6 +52,12 @@
   </si>
   <si>
     <t>0605</t>
+  </si>
+  <si>
+    <t>1402</t>
+  </si>
+  <si>
+    <t>1404</t>
   </si>
 </sst>
 </file>
@@ -439,7 +445,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="2" customWidth="1" collapsed="1"/>
@@ -546,67 +552,72 @@
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>1402</v>
+      <c r="A21" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>1430</v>
+      <c r="A22" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>1502</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>2001</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>2002</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>2004</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>2006</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>2007</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>2013</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>2024</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>2025</v>
       </c>
     </row>
